--- a/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (SPY)_v3.xlsx
+++ b/projects/P_010_Current_Market_Posture/data/excel_exports/History Grid (SPY)_v3.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>High
 Price</t>
@@ -67,11 +67,11 @@
 Price</t>
   </si>
   <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Low
 Price</t>
+  </si>
+  <si>
+    <t>Triple Cross Medium</t>
   </si>
   <si>
     <t>Long
@@ -83,9 +83,6 @@
 Price</t>
   </si>
   <si>
-    <t>Long</t>
-  </si>
-  <si>
     <t>Predicted
 High
 Price</t>
@@ -96,9 +93,6 @@
 Difference</t>
   </si>
   <si>
-    <t>Short</t>
-  </si>
-  <si>
     <t>Volume</t>
   </si>
   <si>
@@ -106,6 +100,9 @@
   </si>
   <si>
     <t>ROC%</t>
+  </si>
+  <si>
+    <t>Triple Cross Short</t>
   </si>
   <si>
     <t>Williams
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Neural Index</t>
+  </si>
+  <si>
+    <t>Triple Cross Long</t>
   </si>
 </sst>
 </file>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -462,13 +462,13 @@
     <col min="8" max="10" width="14.5703125" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
     <col min="12" max="12" width="13.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="17.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="23.7109375" customWidth="1"/>
+    <col min="18" max="18" width="27" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" customWidth="1"/>
     <col min="20" max="22" width="14.5703125" customWidth="1"/>
     <col min="23" max="16384" width="8.7265625"/>
   </cols>
@@ -481,7 +481,7 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -493,28 +493,28 @@
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M1" t="s">
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q1" t="s">
         <v>3</v>
@@ -544,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -567,614 +567,682 @@
     </row>
     <row r="3" ht="19.5" customHeight="1">
       <c r="A3" s="2">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B3">
-        <v>-1.661865234375</v>
+        <v>6.75811767578125</v>
       </c>
       <c r="C3">
-        <v>-3.0921630859375</v>
+        <v>3.67864990234375</v>
       </c>
       <c r="D3">
-        <v>-3.37310791015625</v>
+        <v>0.39495849609375</v>
       </c>
       <c r="E3">
-        <v>760.117004394531</v>
+        <v>766.25</v>
       </c>
       <c r="F3">
-        <v>760.349975585938</v>
+        <v>774.890014648438</v>
       </c>
       <c r="G3">
-        <v>756.150024414063</v>
+        <v>766.030029296875</v>
       </c>
       <c r="H3">
-        <v>757.390014648438</v>
+        <v>773.5</v>
       </c>
       <c r="I3">
-        <v>760.355407714844</v>
+        <v>774.351501464844</v>
       </c>
       <c r="J3">
-        <v>755.11669921875</v>
+        <v>768.979919433594</v>
       </c>
       <c r="K3">
-        <v>46124560</v>
+        <v>50484600</v>
       </c>
       <c r="L3">
-        <v>-0.49462890625</v>
+        <v>0.0314185731112957</v>
       </c>
       <c r="M3">
-        <v>45.9322891235352</v>
+        <v>41.3812561035156</v>
       </c>
       <c r="N3">
-        <v>26.898681640625</v>
+        <v>-27.7011432647705</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>-60.4659996032715</v>
+        <v>100</v>
       </c>
       <c r="Q3">
-        <v>759.766296386719</v>
+        <v>766.538940429688</v>
       </c>
       <c r="R3">
-        <v>762.680297851563</v>
+        <v>763.93408203125</v>
       </c>
       <c r="S3">
-        <v>764.234375</v>
+        <v>763.990234375</v>
       </c>
       <c r="T3">
-        <v>0.00543212890625</v>
+        <v>-0.53851318359375</v>
       </c>
       <c r="U3">
-        <v>-1.0333251953125</v>
+        <v>2.94989013671875</v>
       </c>
       <c r="V3">
-        <v>5.23870849609375</v>
+        <v>5.37158203125</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="2">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B4">
-        <v>-0.8282470703125</v>
+        <v>1.93798828125</v>
       </c>
       <c r="C4">
-        <v>-2.37579345703125</v>
+        <v>-1.1749267578125</v>
       </c>
       <c r="D4">
-        <v>-2.47674560546875</v>
+        <v>-2.816650390625</v>
       </c>
       <c r="E4">
-        <v>759</v>
+        <v>761.309997558594</v>
       </c>
       <c r="F4">
-        <v>763.52001953125</v>
+        <v>762</v>
       </c>
       <c r="G4">
-        <v>757.929992675781</v>
+        <v>757.971008300781</v>
       </c>
       <c r="H4">
-        <v>760.880004882813</v>
+        <v>761.690002441406</v>
       </c>
       <c r="I4">
-        <v>763.031311035156</v>
+        <v>763.255920410156</v>
       </c>
       <c r="J4">
-        <v>757.6845703125</v>
+        <v>759.629943847656</v>
       </c>
       <c r="K4">
-        <v>43992400</v>
+        <v>65395100</v>
       </c>
       <c r="L4">
-        <v>-0.469531834125519</v>
+        <v>-0.473821729421616</v>
       </c>
       <c r="M4">
-        <v>36.1960334777832</v>
+        <v>57.2363891601563</v>
       </c>
       <c r="N4">
-        <v>-12.0678472518921</v>
+        <v>-2.41353273391724</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>-22.0918502807617</v>
+        <v>6.86214685440063</v>
       </c>
       <c r="Q4">
-        <v>761.91455078125</v>
+        <v>760.802368164063</v>
       </c>
       <c r="R4">
-        <v>763.920593261719</v>
+        <v>761.191650390625</v>
       </c>
       <c r="S4">
-        <v>764.855102539063</v>
+        <v>762.919128417969</v>
       </c>
       <c r="T4">
-        <v>-0.48870849609375</v>
+        <v>1.25592041015625</v>
       </c>
       <c r="U4">
-        <v>-0.24542236328125</v>
+        <v>1.658935546875</v>
       </c>
       <c r="V4">
-        <v>5.34674072265625</v>
+        <v>3.6259765625</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="2">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B5">
-        <v>-0.86822509765625</v>
+        <v>0.8887939453125</v>
       </c>
       <c r="C5">
-        <v>-2.2158203125</v>
+        <v>-3.1492919921875</v>
       </c>
       <c r="D5">
-        <v>-1.8809814453125</v>
+        <v>-3.78399658203125</v>
       </c>
       <c r="E5">
-        <v>764.719970703125</v>
+        <v>763.150024414063</v>
       </c>
       <c r="F5">
-        <v>766.380004882813</v>
+        <v>763.570007324219</v>
       </c>
       <c r="G5">
-        <v>763.599975585938</v>
+        <v>759.960021972656</v>
       </c>
       <c r="H5">
-        <v>764.289978027344</v>
+        <v>762.599975585938</v>
       </c>
       <c r="I5">
-        <v>766.980834960938</v>
+        <v>766.506103515625</v>
       </c>
       <c r="J5">
-        <v>762.802551269531</v>
+        <v>760.861206054688</v>
       </c>
       <c r="K5">
-        <v>45512700</v>
+        <v>49652700</v>
       </c>
       <c r="L5">
-        <v>-0.415722072124481</v>
+        <v>-0.553821384906769</v>
       </c>
       <c r="M5">
-        <v>41.1635932922363</v>
+        <v>58.6519737243652</v>
       </c>
       <c r="N5">
-        <v>-4.78356552124023</v>
+        <v>-7.17874240875244</v>
       </c>
       <c r="O5" t="s">
         <v>1</v>
       </c>
       <c r="P5">
-        <v>63.0665969848633</v>
+        <v>74.0647430419922</v>
       </c>
       <c r="Q5">
-        <v>763.298156738281</v>
+        <v>760.072509765625</v>
       </c>
       <c r="R5">
-        <v>764.75390625</v>
+        <v>761.038879394531</v>
       </c>
       <c r="S5">
-        <v>765.342163085938</v>
+        <v>763.073303222656</v>
       </c>
       <c r="T5">
-        <v>0.600830078125</v>
+        <v>2.93609619140625</v>
       </c>
       <c r="U5">
-        <v>-0.79742431640625</v>
+        <v>0.90118408203125</v>
       </c>
       <c r="V5">
-        <v>4.17828369140625</v>
+        <v>5.6448974609375</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="2">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B6">
-        <v>-5.49237060546875</v>
+        <v>-3.3385009765625</v>
       </c>
       <c r="C6">
-        <v>-3.8779296875</v>
+        <v>-5.25146484375</v>
       </c>
       <c r="D6">
-        <v>-2.16845703125</v>
+        <v>-4.92291259765625</v>
       </c>
       <c r="E6">
-        <v>758.030029296875</v>
+        <v>759.5</v>
       </c>
       <c r="F6">
-        <v>760.109985351563</v>
+        <v>761.669982910156</v>
       </c>
       <c r="G6">
-        <v>756.640014648438</v>
+        <v>749.599975585938</v>
       </c>
       <c r="H6">
-        <v>757.830017089844</v>
+        <v>754.049987792969</v>
       </c>
       <c r="I6">
-        <v>760.855407714844</v>
+        <v>757.408813476563</v>
       </c>
       <c r="J6">
-        <v>756.68115234375</v>
+        <v>750.171142578125</v>
       </c>
       <c r="K6">
-        <v>42740300</v>
+        <v>59217600</v>
       </c>
       <c r="L6">
-        <v>-0.500962018966675</v>
+        <v>-0.587152361869812</v>
       </c>
       <c r="M6">
-        <v>43.2316055297852</v>
+        <v>63.1880836486816</v>
       </c>
       <c r="N6">
-        <v>-0.76812744140625</v>
+        <v>37.546817779541</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>-71.4563598632813</v>
+        <v>-75.5807952880859</v>
       </c>
       <c r="Q6">
-        <v>761.900756835938</v>
+        <v>756.818969726563</v>
       </c>
       <c r="R6">
-        <v>764.700561523438</v>
+        <v>760.635131835938</v>
       </c>
       <c r="S6">
-        <v>765.38232421875</v>
+        <v>763.134765625</v>
       </c>
       <c r="T6">
-        <v>0.74542236328125</v>
+        <v>-4.26116943359375</v>
       </c>
       <c r="U6">
-        <v>0.0411376953125</v>
+        <v>0.5711669921875</v>
       </c>
       <c r="V6">
-        <v>4.17425537109375</v>
+        <v>7.2376708984375</v>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="2">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B7">
-        <v>-3.032958984375</v>
+        <v>-1.661865234375</v>
       </c>
       <c r="C7">
-        <v>-1.5882568359375</v>
+        <v>-3.0921630859375</v>
       </c>
       <c r="D7">
-        <v>-0.46343994140625</v>
+        <v>-3.37310791015625</v>
       </c>
       <c r="E7">
-        <v>764.080017089844</v>
+        <v>760.119995117188</v>
       </c>
       <c r="F7">
-        <v>764.469970703125</v>
+        <v>760.349975585938</v>
       </c>
       <c r="G7">
-        <v>760.940002441406</v>
+        <v>756.150024414063</v>
       </c>
       <c r="H7">
-        <v>762.400024414063</v>
+        <v>757.390014648438</v>
       </c>
       <c r="I7">
-        <v>765.176208496094</v>
+        <v>760.355407714844</v>
       </c>
       <c r="J7">
-        <v>760.601745605469</v>
+        <v>755.11669921875</v>
       </c>
       <c r="K7">
-        <v>32812400</v>
+        <v>46194900</v>
       </c>
       <c r="L7">
-        <v>-0.680486798286438</v>
+        <v>-0.494771331548691</v>
       </c>
       <c r="M7">
-        <v>43.5662498474121</v>
+        <v>45.9393272399902</v>
       </c>
       <c r="N7">
-        <v>-9.16973114013672</v>
+        <v>26.9181251525879</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P7">
-        <v>-78.3713836669922</v>
+        <v>-60.4659996032715</v>
       </c>
       <c r="Q7">
-        <v>765.345336914063</v>
+        <v>759.766296386719</v>
       </c>
       <c r="R7">
-        <v>766.651306152344</v>
+        <v>762.680297851563</v>
       </c>
       <c r="S7">
-        <v>766.266052246094</v>
+        <v>764.234375</v>
       </c>
       <c r="T7">
-        <v>0.70623779296875</v>
+        <v>0.00543212890625</v>
       </c>
       <c r="U7">
-        <v>-0.3382568359375</v>
+        <v>-1.0333251953125</v>
       </c>
       <c r="V7">
-        <v>4.574462890625</v>
+        <v>5.23870849609375</v>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="2">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B8">
-        <v>0.3255615234375</v>
+        <v>-0.8282470703125</v>
       </c>
       <c r="C8">
-        <v>0.6226806640625</v>
+        <v>-2.37579345703125</v>
       </c>
       <c r="D8">
-        <v>1.06060791015625</v>
+        <v>-2.47674560546875</v>
       </c>
       <c r="E8">
-        <v>769.070007324219</v>
+        <v>759</v>
       </c>
       <c r="F8">
-        <v>769.700012207031</v>
+        <v>763.52001953125</v>
       </c>
       <c r="G8">
-        <v>765.140014648438</v>
+        <v>757.929992675781</v>
       </c>
       <c r="H8">
-        <v>765.960021972656</v>
+        <v>760.880004882813</v>
       </c>
       <c r="I8">
-        <v>768.510559082031</v>
+        <v>763.031311035156</v>
       </c>
       <c r="J8">
-        <v>763.835144042969</v>
+        <v>757.6845703125</v>
       </c>
       <c r="K8">
-        <v>44746000</v>
+        <v>43992400</v>
       </c>
       <c r="L8">
-        <v>-0.580008387565613</v>
+        <v>-0.469531834125519</v>
       </c>
       <c r="M8">
-        <v>47.9644622802734</v>
+        <v>36.1960334777832</v>
       </c>
       <c r="N8">
-        <v>10.858211517334</v>
+        <v>-12.0678472518921</v>
       </c>
       <c r="O8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P8">
-        <v>-75.2247161865234</v>
+        <v>-22.0918502807617</v>
       </c>
       <c r="Q8">
-        <v>767.962890625</v>
+        <v>761.91455078125</v>
       </c>
       <c r="R8">
-        <v>768.026000976563</v>
+        <v>763.920593261719</v>
       </c>
       <c r="S8">
-        <v>766.837463378906</v>
+        <v>764.855102539063</v>
       </c>
       <c r="T8">
-        <v>-1.189453125</v>
+        <v>-0.48870849609375</v>
       </c>
       <c r="U8">
-        <v>-1.30487060546875</v>
+        <v>-0.24542236328125</v>
       </c>
       <c r="V8">
-        <v>4.6754150390625</v>
+        <v>5.34674072265625</v>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="2">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="B9">
-        <v>3.0567626953125</v>
+        <v>-0.86822509765625</v>
       </c>
       <c r="C9">
-        <v>2.2767333984375</v>
+        <v>-2.2158203125</v>
       </c>
       <c r="D9">
-        <v>1.39373779296875</v>
+        <v>-1.8809814453125</v>
       </c>
       <c r="E9">
-        <v>772.010009765625</v>
+        <v>764.719970703125</v>
       </c>
       <c r="F9">
-        <v>772.869995117188</v>
+        <v>766.380004882813</v>
       </c>
       <c r="G9">
-        <v>769</v>
+        <v>763.599975585938</v>
       </c>
       <c r="H9">
-        <v>770.190002441406</v>
+        <v>764.289978027344</v>
       </c>
       <c r="I9">
-        <v>773.0634765625</v>
+        <v>766.980834960938</v>
       </c>
       <c r="J9">
-        <v>769.054077148438</v>
+        <v>762.802551269531</v>
       </c>
       <c r="K9">
-        <v>34054200</v>
+        <v>45512700</v>
       </c>
       <c r="L9">
-        <v>-0.32524761557579</v>
+        <v>-0.415722072124481</v>
       </c>
       <c r="M9">
-        <v>43.2664947509766</v>
+        <v>41.1635932922363</v>
       </c>
       <c r="N9">
-        <v>3.37308049201965</v>
+        <v>-4.78356552124023</v>
       </c>
       <c r="O9" t="s">
         <v>1</v>
       </c>
       <c r="P9">
-        <v>18.508508682251</v>
+        <v>63.0665969848633</v>
       </c>
       <c r="Q9">
-        <v>769.826171875</v>
+        <v>763.298156738281</v>
       </c>
       <c r="R9">
-        <v>768.584777832031</v>
+        <v>764.75390625</v>
       </c>
       <c r="S9">
-        <v>766.935974121094</v>
+        <v>765.342163085938</v>
       </c>
       <c r="T9">
-        <v>0.1934814453125</v>
+        <v>0.600830078125</v>
       </c>
       <c r="U9">
-        <v>0.0540771484375</v>
+        <v>-0.79742431640625</v>
       </c>
       <c r="V9">
-        <v>4.0093994140625</v>
+        <v>4.17828369140625</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="2">
-        <v>46268</v>
+        <v>46275</v>
       </c>
       <c r="B10">
-        <v>2.73944091796875</v>
+        <v>-5.49237060546875</v>
       </c>
       <c r="C10">
-        <v>1.54052734375</v>
+        <v>-3.8779296875</v>
       </c>
       <c r="D10">
-        <v>-0.019287109375</v>
+        <v>-2.16845703125</v>
       </c>
       <c r="E10">
-        <v>767.900024414063</v>
+        <v>758.030029296875</v>
       </c>
       <c r="F10">
-        <v>774.030029296875</v>
+        <v>760.109985351563</v>
       </c>
       <c r="G10">
-        <v>767.450012207031</v>
+        <v>756.640014648438</v>
       </c>
       <c r="H10">
-        <v>773.169982910156</v>
+        <v>757.830017089844</v>
       </c>
       <c r="I10">
-        <v>775.129516601563</v>
+        <v>760.855407714844</v>
       </c>
       <c r="J10">
-        <v>769.539184570313</v>
+        <v>756.68115234375</v>
       </c>
       <c r="K10">
-        <v>43531500</v>
+        <v>42740300</v>
       </c>
       <c r="L10">
-        <v>-0.317153215408325</v>
+        <v>-0.500962018966675</v>
       </c>
       <c r="M10">
-        <v>41.8547019958496</v>
+        <v>43.2316055297852</v>
       </c>
       <c r="N10">
-        <v>-36.0535163879395</v>
+        <v>-0.76812744140625</v>
       </c>
       <c r="O10" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="P10">
-        <v>99.9999923706055</v>
+        <v>-71.4563598632813</v>
       </c>
       <c r="Q10">
-        <v>768.88037109375</v>
+        <v>761.900756835938</v>
       </c>
       <c r="R10">
-        <v>767.789794921875</v>
+        <v>764.700561523438</v>
       </c>
       <c r="S10">
-        <v>766.40087890625</v>
+        <v>765.38232421875</v>
       </c>
       <c r="T10">
-        <v>1.0994873046875</v>
+        <v>0.74542236328125</v>
       </c>
       <c r="U10">
-        <v>2.08917236328125</v>
+        <v>0.0411376953125</v>
       </c>
       <c r="V10">
-        <v>5.59033203125</v>
+        <v>4.17425537109375</v>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="2">
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="B11">
-        <v>-1.99066162109375</v>
+        <v>-3.032958984375</v>
       </c>
       <c r="C11">
-        <v>-0.54931640625</v>
+        <v>-1.5882568359375</v>
       </c>
       <c r="D11">
-        <v>-2.27935791015625</v>
+        <v>-0.46343994140625</v>
       </c>
       <c r="E11">
-        <v>762.450012207031</v>
+        <v>764.080017089844</v>
       </c>
       <c r="F11">
-        <v>766.429992675781</v>
+        <v>764.469970703125</v>
       </c>
       <c r="G11">
-        <v>761.72998046875</v>
+        <v>760.940002441406</v>
       </c>
       <c r="H11">
-        <v>765.159973144531</v>
+        <v>762.400024414063</v>
       </c>
       <c r="I11">
-        <v>767.979614257813</v>
+        <v>765.176208496094</v>
       </c>
       <c r="J11">
-        <v>763.237609863281</v>
+        <v>760.601745605469</v>
       </c>
       <c r="K11">
-        <v>29566200</v>
+        <v>32812400</v>
       </c>
       <c r="L11">
-        <v>-0.856674909591675</v>
+        <v>-0.680486798286438</v>
       </c>
       <c r="M11">
-        <v>65.4527053833008</v>
+        <v>43.5662498474121</v>
       </c>
       <c r="N11">
-        <v>-17.6047134399414</v>
+        <v>-9.16973114013672</v>
       </c>
       <c r="O11" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="P11">
-        <v>9.29729080200195</v>
+        <v>-78.3713836669922</v>
       </c>
       <c r="Q11">
-        <v>765.153686523438</v>
+        <v>765.345336914063</v>
       </c>
       <c r="R11">
-        <v>766.204406738281</v>
+        <v>766.651306152344</v>
       </c>
       <c r="S11">
-        <v>765.59033203125</v>
+        <v>766.266052246094</v>
       </c>
       <c r="T11">
-        <v>1.54962158203125</v>
+        <v>0.70623779296875</v>
       </c>
       <c r="U11">
-        <v>1.50762939453125</v>
+        <v>-0.3382568359375</v>
       </c>
       <c r="V11">
-        <v>4.74200439453125</v>
+        <v>4.574462890625</v>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B12">
+        <v>0.3255615234375</v>
+      </c>
+      <c r="C12">
+        <v>0.6226806640625</v>
+      </c>
+      <c r="D12">
+        <v>1.06060791015625</v>
+      </c>
+      <c r="E12">
+        <v>769.070007324219</v>
+      </c>
+      <c r="F12">
+        <v>769.700012207031</v>
+      </c>
+      <c r="G12">
+        <v>765.140014648438</v>
+      </c>
+      <c r="H12">
+        <v>765.960021972656</v>
+      </c>
+      <c r="I12">
+        <v>768.510559082031</v>
+      </c>
+      <c r="J12">
+        <v>763.835144042969</v>
+      </c>
+      <c r="K12">
+        <v>44746000</v>
+      </c>
+      <c r="L12">
+        <v>-0.580008387565613</v>
+      </c>
+      <c r="M12">
+        <v>47.9644622802734</v>
+      </c>
+      <c r="N12">
+        <v>10.858211517334</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12">
+        <v>-75.2247161865234</v>
+      </c>
+      <c r="Q12">
+        <v>767.962890625</v>
+      </c>
+      <c r="R12">
+        <v>768.026000976563</v>
+      </c>
+      <c r="S12">
+        <v>766.837463378906</v>
+      </c>
+      <c r="T12">
+        <v>-1.189453125</v>
+      </c>
+      <c r="U12">
+        <v>-1.30487060546875</v>
+      </c>
+      <c r="V12">
+        <v>4.6754150390625</v>
       </c>
     </row>
   </sheetData>
